--- a/Suppl/pPCA_results_with_PGLS.xlsx
+++ b/Suppl/pPCA_results_with_PGLS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pcriz\OneDrive\Desktop\New iteration placenta life history\Suppl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E3E1F3-CE87-4B2B-B870-F26678EA7603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898082D7-4FFD-412B-AC35-171523C7D081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pPCA_variance" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="437">
   <si>
     <t>PC</t>
   </si>
@@ -1436,41 +1436,17 @@
   </cellStyles>
   <dxfs count="9">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -1496,20 +1472,6 @@
           <bgColor theme="4"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1583,6 +1545,44 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1597,7 +1597,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F13F2519-7F27-4DED-A1CE-B0726A4CD5BE}" name="Table2" displayName="Table2" ref="A1:D5" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F13F2519-7F27-4DED-A1CE-B0726A4CD5BE}" name="Table2" displayName="Table2" ref="A1:D5" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A1:D5" xr:uid="{F13F2519-7F27-4DED-A1CE-B0726A4CD5BE}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{72CE0B67-4E1C-4976-B9B5-1D5F50F0D611}" name="PC"/>
@@ -1610,7 +1610,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E85F7153-033C-4818-B86F-237469EA1AC2}" name="Table4" displayName="Table4" ref="A1:G375" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E85F7153-033C-4818-B86F-237469EA1AC2}" name="Table4" displayName="Table4" ref="A1:G375" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:G375" xr:uid="{E85F7153-033C-4818-B86F-237469EA1AC2}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{5C94FECA-1747-4074-918F-F6A6962EEB52}" name="PC1"/>
@@ -1626,7 +1626,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D83FBB4A-C320-4F2C-BF02-1217FE4C7DF8}" name="Table3" displayName="Table3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D83FBB4A-C320-4F2C-BF02-1217FE4C7DF8}" name="Table3" displayName="Table3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="A1:E5" xr:uid="{D83FBB4A-C320-4F2C-BF02-1217FE4C7DF8}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{FF9CD2A4-37A4-4FE7-BEB9-79373A77216C}" name="trait"/>
@@ -1640,14 +1640,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E509E5C6-8D5F-4E17-8912-EADC132D3073}" name="Table1" displayName="Table1" ref="A1:F33" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="5">
-  <autoFilter ref="A1:F33" xr:uid="{E509E5C6-8D5F-4E17-8912-EADC132D3073}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E509E5C6-8D5F-4E17-8912-EADC132D3073}" name="Table1" displayName="Table1" ref="A1:E33" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:E33" xr:uid="{E509E5C6-8D5F-4E17-8912-EADC132D3073}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{FA8F5C82-6D9C-47DD-AE05-84212BDB0C50}" name="model"/>
     <tableColumn id="2" xr3:uid="{C4FCB7A3-BCF6-4FDD-A3E1-B9393931298B}" name="term"/>
     <tableColumn id="3" xr3:uid="{9C0BF716-A0E2-4850-A808-9E7073457994}" name="Value"/>
     <tableColumn id="4" xr3:uid="{6139B619-1BBD-4D36-99A3-9EC65D564096}" name="Std.Error"/>
-    <tableColumn id="5" xr3:uid="{EA2BDC4A-B2EA-4835-BD0E-F28493240383}" name="t-value"/>
     <tableColumn id="6" xr3:uid="{1B1B53D1-4496-45B1-B8BA-5133A9412ABE}" name="p-value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1655,7 +1654,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E16765A3-3046-472E-B268-D4DBDE169E94}" name="Table5" displayName="Table5" ref="A1:F33" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E16765A3-3046-472E-B268-D4DBDE169E94}" name="Table5" displayName="Table5" ref="A1:F33" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:F33" xr:uid="{E16765A3-3046-472E-B268-D4DBDE169E94}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{6961F5EA-17EE-4D2B-96BC-96E35A3088C5}" name="model"/>
@@ -10785,17 +10784,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB425647-6EA8-44D9-837D-07686C3D7EFE}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
     <col min="2" max="2" width="33.7265625" customWidth="1"/>
     <col min="4" max="4" width="10.26953125" customWidth="1"/>
-    <col min="5" max="5" width="8.90625" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>428</v>
       </c>
@@ -10808,14 +10806,11 @@
       <c r="D1" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>404</v>
       </c>
@@ -10829,13 +10824,10 @@
         <v>0.425026028</v>
       </c>
       <c r="E2">
-        <v>-1.9681149090000001</v>
-      </c>
-      <c r="F2">
         <v>4.9799113999999998E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>404</v>
       </c>
@@ -10849,13 +10841,10 @@
         <v>0.157590549</v>
       </c>
       <c r="E3">
-        <v>2.2630172910000002</v>
-      </c>
-      <c r="F3">
         <v>2.4212022E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>404</v>
       </c>
@@ -10869,13 +10858,10 @@
         <v>0.30195302400000001</v>
       </c>
       <c r="E4">
-        <v>3.9134461749999998</v>
-      </c>
-      <c r="F4">
         <v>1.0823999999999999E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>407</v>
       </c>
@@ -10889,13 +10875,10 @@
         <v>0.435710231</v>
       </c>
       <c r="E5">
-        <v>-0.53676748900000004</v>
-      </c>
-      <c r="F5">
         <v>0.59174996499999999</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>407</v>
       </c>
@@ -10909,13 +10892,10 @@
         <v>0.340610845</v>
       </c>
       <c r="E6">
-        <v>0.76821185599999997</v>
-      </c>
-      <c r="F6">
         <v>0.44285002499999998</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>407</v>
       </c>
@@ -10929,13 +10909,10 @@
         <v>0.23370048500000001</v>
       </c>
       <c r="E7">
-        <v>1.134508651</v>
-      </c>
-      <c r="F7">
         <v>0.25731372800000002</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>410</v>
       </c>
@@ -10948,14 +10925,11 @@
       <c r="D8">
         <v>0.33010621400000001</v>
       </c>
-      <c r="E8">
-        <v>8.5457495350000006</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>410</v>
       </c>
@@ -10969,13 +10943,10 @@
         <v>0.121381365</v>
       </c>
       <c r="E9">
-        <v>2.8170020720000002</v>
-      </c>
-      <c r="F9">
         <v>5.107388E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>410</v>
       </c>
@@ -10989,13 +10960,10 @@
         <v>0.20463015400000001</v>
       </c>
       <c r="E10">
-        <v>3.0634707900000002</v>
-      </c>
-      <c r="F10">
         <v>2.3481259999999999E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>410</v>
       </c>
@@ -11008,14 +10976,11 @@
       <c r="D11">
         <v>2.0522261999999999E-2</v>
       </c>
-      <c r="E11">
-        <v>-20.852740010000002</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>413</v>
       </c>
@@ -11028,14 +10993,11 @@
       <c r="D12">
         <v>0.34446225200000002</v>
       </c>
-      <c r="E12">
-        <v>9.4332311949999994</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>413</v>
       </c>
@@ -11049,13 +11011,10 @@
         <v>0.247101815</v>
       </c>
       <c r="E13">
-        <v>0.325470598</v>
-      </c>
-      <c r="F13">
         <v>0.74500890500000005</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>413</v>
       </c>
@@ -11069,13 +11028,10 @@
         <v>0.19206368800000001</v>
       </c>
       <c r="E14">
-        <v>0.74299143599999995</v>
-      </c>
-      <c r="F14">
         <v>0.45795833899999999</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>413</v>
       </c>
@@ -11088,14 +11044,11 @@
       <c r="D15">
         <v>2.0711586000000001E-2</v>
       </c>
-      <c r="E15">
-        <v>-21.071500660000002</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>416</v>
       </c>
@@ -11108,14 +11061,11 @@
       <c r="D16">
         <v>0.82394913199999997</v>
       </c>
-      <c r="E16">
-        <v>5.1278810129999997</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>416</v>
       </c>
@@ -11129,13 +11079,10 @@
         <v>0.15930072100000001</v>
       </c>
       <c r="E17">
-        <v>2.39760069</v>
-      </c>
-      <c r="F17">
         <v>1.6997834999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>416</v>
       </c>
@@ -11149,13 +11096,10 @@
         <v>0.284191535</v>
       </c>
       <c r="E18">
-        <v>3.313909717</v>
-      </c>
-      <c r="F18">
         <v>1.0108459999999999E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>416</v>
       </c>
@@ -11168,14 +11112,11 @@
       <c r="D19">
         <v>8.0368893999999996E-2</v>
       </c>
-      <c r="E19">
-        <v>-7.0049834879999997</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>419</v>
       </c>
@@ -11188,14 +11129,11 @@
       <c r="D20">
         <v>0.86244625799999997</v>
       </c>
-      <c r="E20">
-        <v>5.9353704240000003</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>419</v>
       </c>
@@ -11209,13 +11147,10 @@
         <v>0.33437473699999998</v>
       </c>
       <c r="E21">
-        <v>0.18426394300000001</v>
-      </c>
-      <c r="F21">
         <v>0.85390734599999996</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>419</v>
       </c>
@@ -11229,13 +11164,10 @@
         <v>0.24929504899999999</v>
       </c>
       <c r="E22">
-        <v>0.287352259</v>
-      </c>
-      <c r="F22">
         <v>0.77400347700000005</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>419</v>
       </c>
@@ -11248,14 +11180,11 @@
       <c r="D23">
         <v>8.2566127000000003E-2</v>
       </c>
-      <c r="E23">
-        <v>-7.1975995069999996</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>422</v>
       </c>
@@ -11268,14 +11197,11 @@
       <c r="D24">
         <v>0.599264032</v>
       </c>
-      <c r="E24">
-        <v>6.7354715150000004</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>422</v>
       </c>
@@ -11289,13 +11215,10 @@
         <v>0.122375626</v>
       </c>
       <c r="E25">
-        <v>2.808687205</v>
-      </c>
-      <c r="F25">
         <v>5.2390120000000004E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>422</v>
       </c>
@@ -11309,13 +11232,10 @@
         <v>0.20344491000000001</v>
       </c>
       <c r="E26">
-        <v>2.8628428239999999</v>
-      </c>
-      <c r="F26">
         <v>4.4382179999999999E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>422</v>
       </c>
@@ -11329,13 +11249,10 @@
         <v>6.3932201999999994E-2</v>
       </c>
       <c r="E27">
-        <v>-2.3899520270000001</v>
-      </c>
-      <c r="F27">
         <v>1.7351686000000002E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>422</v>
       </c>
@@ -11348,14 +11265,11 @@
       <c r="D28">
         <v>2.2103979999999999E-2</v>
       </c>
-      <c r="E28">
-        <v>-18.503168559999999</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>425</v>
       </c>
@@ -11368,14 +11282,11 @@
       <c r="D29">
         <v>0.63048230199999999</v>
       </c>
-      <c r="E29">
-        <v>7.2894089209999997</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>425</v>
       </c>
@@ -11389,13 +11300,10 @@
         <v>0.24822517499999999</v>
       </c>
       <c r="E30">
-        <v>9.1581724000000003E-2</v>
-      </c>
-      <c r="F30">
         <v>0.92708006899999995</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>425</v>
       </c>
@@ -11409,13 +11317,10 @@
         <v>0.19658353000000001</v>
       </c>
       <c r="E31">
-        <v>0.42003780200000002</v>
-      </c>
-      <c r="F31">
         <v>0.67470230899999994</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>425</v>
       </c>
@@ -11429,13 +11334,10 @@
         <v>6.5737274999999998E-2</v>
       </c>
       <c r="E32">
-        <v>-2.5360806039999999</v>
-      </c>
-      <c r="F32">
         <v>1.1621786E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>425</v>
       </c>
@@ -11448,10 +11350,7 @@
       <c r="D33">
         <v>2.2354895E-2</v>
       </c>
-      <c r="E33">
-        <v>-18.598779879999999</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>427</v>
       </c>
     </row>
